--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-FrAllergieOuHypersensibilite.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-FrAllergieOuHypersensibilite.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3227" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3227" uniqueCount="339">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T14:36:02+00:00</t>
+    <t>2025-06-05T15:38:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -882,12 +882,7 @@
     <t>Observation.value</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/ANY
-http://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
-  </si>
-  <si>
-    <t>L'élément &lt;value&gt; sera utilisé pour indiquer qu'il n'y a pas d'allergie/hypersensibilité ou que l'on ne sait pas à partir du jdv-absent-or-unknown-allergy-cisis (1.2.250.1.213.1.1.5.661). 
- - Type : CD</t>
+    <t>L'élément &lt;value&gt; sera utilisé pour indiquer qu'il n'y a pas d'allergie/hypersensibilité ou que l'on ne sait pas à partir du jdv-absent-or-unknown-allergy-cisis (1.2.250.1.213.1.1.5.661).</t>
   </si>
   <si>
     <t>Observation.interpretationCode</t>
@@ -1393,7 +1388,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="130.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -8696,10 +8691,10 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -8771,10 +8766,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8830,7 +8825,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -8848,7 +8843,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8868,10 +8863,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8927,7 +8922,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>74</v>
@@ -8945,7 +8940,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8965,10 +8960,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8995,7 +8990,7 @@
       </c>
       <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9046,7 +9041,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9066,10 +9061,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9092,7 +9087,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9145,7 +9140,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9165,10 +9160,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9191,7 +9186,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9244,7 +9239,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9264,10 +9259,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9290,7 +9285,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9343,7 +9338,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9363,10 +9358,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9389,7 +9384,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9442,7 +9437,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9462,10 +9457,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9488,7 +9483,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9541,7 +9536,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9561,10 +9556,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9587,10 +9582,10 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -9642,7 +9637,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9662,10 +9657,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9688,7 +9683,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9729,7 +9724,7 @@
         <v>74</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AC82" s="2"/>
       <c r="AD82" t="s" s="2">
@@ -9739,7 +9734,7 @@
         <v>123</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9759,13 +9754,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C83" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>74</v>
@@ -9787,10 +9782,10 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -9842,7 +9837,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9862,13 +9857,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>74</v>
@@ -9890,10 +9885,10 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
@@ -9945,7 +9940,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9965,13 +9960,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C85" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>74</v>
@@ -9993,10 +9988,10 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -10048,7 +10043,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10068,13 +10063,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C86" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>74</v>
@@ -10096,10 +10091,10 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -10151,7 +10146,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10171,10 +10166,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10197,7 +10192,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10250,7 +10245,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10270,10 +10265,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10296,7 +10291,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10349,7 +10344,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10369,10 +10364,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10395,7 +10390,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10448,7 +10443,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10468,10 +10463,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10494,11 +10489,11 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10549,7 +10544,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10569,10 +10564,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10670,10 +10665,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10771,10 +10766,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10872,10 +10867,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10973,10 +10968,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11076,10 +11071,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11179,10 +11174,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11282,10 +11277,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11385,10 +11380,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11486,10 +11481,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11523,7 +11518,7 @@
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>74</v>
@@ -11545,7 +11540,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>74</v>
@@ -11563,7 +11558,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11583,10 +11578,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11609,7 +11604,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11662,7 +11657,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -11682,10 +11677,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11708,7 +11703,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -11761,7 +11756,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-FrAllergieOuHypersensibilite.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-FrAllergieOuHypersensibilite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
